--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285800</v>
+        <v>120285805</v>
       </c>
       <c r="B2" t="n">
-        <v>56522</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468599</v>
+        <v>468715</v>
       </c>
       <c r="R2" t="n">
-        <v>6546558</v>
+        <v>6546633</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285801</v>
+        <v>120285800</v>
       </c>
       <c r="B3" t="n">
-        <v>89633</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +797,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468586</v>
+        <v>468599</v>
       </c>
       <c r="R3" t="n">
-        <v>6546480</v>
+        <v>6546558</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -893,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120285805</v>
+        <v>120285803</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,42 +908,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468715</v>
+        <v>468607</v>
       </c>
       <c r="R4" t="n">
-        <v>6546633</v>
+        <v>6546581</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120285803</v>
+        <v>120285804</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>97847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,35 +1015,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468607</v>
+        <v>468660</v>
       </c>
       <c r="R5" t="n">
-        <v>6546581</v>
+        <v>6546604</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120285804</v>
+        <v>120285801</v>
       </c>
       <c r="B6" t="n">
-        <v>97824</v>
+        <v>89650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,35 +1126,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468660</v>
+        <v>468586</v>
       </c>
       <c r="R6" t="n">
-        <v>6546604</v>
+        <v>6546480</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,7 +1228,7 @@
         <v>120285799</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>120285802</v>
       </c>
       <c r="B8" t="n">
-        <v>94574</v>
+        <v>94597</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285805</v>
+        <v>120285804</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>97847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468715</v>
+        <v>468660</v>
       </c>
       <c r="R2" t="n">
-        <v>6546633</v>
+        <v>6546604</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285800</v>
+        <v>120285801</v>
       </c>
       <c r="B3" t="n">
-        <v>56532</v>
+        <v>89650</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468599</v>
+        <v>468586</v>
       </c>
       <c r="R3" t="n">
-        <v>6546558</v>
+        <v>6546480</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1003,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120285804</v>
+        <v>120285805</v>
       </c>
       <c r="B5" t="n">
-        <v>97847</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,47 +1020,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468660</v>
+        <v>468715</v>
       </c>
       <c r="R5" t="n">
-        <v>6546604</v>
+        <v>6546633</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120285801</v>
+        <v>120285799</v>
       </c>
       <c r="B6" t="n">
-        <v>89650</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,9 +1156,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468586</v>
+        <v>468719</v>
       </c>
       <c r="R6" t="n">
-        <v>6546480</v>
+        <v>6546629</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120285799</v>
+        <v>120285800</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,35 +1241,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468719</v>
+        <v>468599</v>
       </c>
       <c r="R7" t="n">
-        <v>6546629</v>
+        <v>6546558</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120285803</v>
+        <v>120285799</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -935,9 +935,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468607</v>
+        <v>468719</v>
       </c>
       <c r="R4" t="n">
-        <v>6546581</v>
+        <v>6546629</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120285805</v>
+        <v>120285803</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,42 +1024,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468715</v>
+        <v>468607</v>
       </c>
       <c r="R5" t="n">
-        <v>6546633</v>
+        <v>6546581</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1118,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120285799</v>
+        <v>120285800</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,35 +1131,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468719</v>
+        <v>468599</v>
       </c>
       <c r="R6" t="n">
-        <v>6546629</v>
+        <v>6546558</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1229,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120285800</v>
+        <v>120285805</v>
       </c>
       <c r="B7" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,43 +1238,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468599</v>
+        <v>468715</v>
       </c>
       <c r="R7" t="n">
-        <v>6546558</v>
+        <v>6546633</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285804</v>
+        <v>120285799</v>
       </c>
       <c r="B2" t="n">
-        <v>97847</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468660</v>
+        <v>468719</v>
       </c>
       <c r="R2" t="n">
-        <v>6546604</v>
+        <v>6546629</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120285799</v>
+        <v>120285800</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468719</v>
+        <v>468599</v>
       </c>
       <c r="R4" t="n">
-        <v>6546629</v>
+        <v>6546558</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120285803</v>
+        <v>120285804</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>97847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1016,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1057,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468607</v>
+        <v>468660</v>
       </c>
       <c r="R5" t="n">
-        <v>6546581</v>
+        <v>6546604</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120285800</v>
+        <v>120285805</v>
       </c>
       <c r="B6" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,43 +1127,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468599</v>
+        <v>468715</v>
       </c>
       <c r="R6" t="n">
-        <v>6546558</v>
+        <v>6546633</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120285805</v>
+        <v>120285803</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,42 +1241,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468715</v>
+        <v>468607</v>
       </c>
       <c r="R7" t="n">
-        <v>6546633</v>
+        <v>6546581</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285799</v>
+        <v>120285805</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,26 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468719</v>
+        <v>468715</v>
       </c>
       <c r="R2" t="n">
-        <v>6546629</v>
+        <v>6546633</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285801</v>
+        <v>120285800</v>
       </c>
       <c r="B3" t="n">
-        <v>89650</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +797,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468586</v>
+        <v>468599</v>
       </c>
       <c r="R3" t="n">
-        <v>6546480</v>
+        <v>6546558</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120285800</v>
+        <v>120285799</v>
       </c>
       <c r="B4" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,31 +904,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468599</v>
+        <v>468719</v>
       </c>
       <c r="R4" t="n">
-        <v>6546558</v>
+        <v>6546629</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120285804</v>
+        <v>120285803</v>
       </c>
       <c r="B5" t="n">
-        <v>97847</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,35 +1015,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1053,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468660</v>
+        <v>468607</v>
       </c>
       <c r="R5" t="n">
-        <v>6546604</v>
+        <v>6546581</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120285805</v>
+        <v>120285801</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>89650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,42 +1130,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468715</v>
+        <v>468586</v>
       </c>
       <c r="R6" t="n">
-        <v>6546633</v>
+        <v>6546480</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120285803</v>
+        <v>120285804</v>
       </c>
       <c r="B7" t="n">
-        <v>78278</v>
+        <v>97847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,35 +1237,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468607</v>
+        <v>468660</v>
       </c>
       <c r="R7" t="n">
-        <v>6546581</v>
+        <v>6546604</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285805</v>
+        <v>120285801</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>89650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468715</v>
+        <v>468586</v>
       </c>
       <c r="R2" t="n">
-        <v>6546633</v>
+        <v>6546480</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285800</v>
+        <v>120285804</v>
       </c>
       <c r="B3" t="n">
-        <v>56532</v>
+        <v>97847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,27 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468599</v>
+        <v>468660</v>
       </c>
       <c r="R3" t="n">
-        <v>6546558</v>
+        <v>6546604</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1114,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120285801</v>
+        <v>120285800</v>
       </c>
       <c r="B6" t="n">
-        <v>89650</v>
+        <v>56532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,35 +1131,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468586</v>
+        <v>468599</v>
       </c>
       <c r="R6" t="n">
-        <v>6546480</v>
+        <v>6546558</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120285804</v>
+        <v>120285805</v>
       </c>
       <c r="B7" t="n">
-        <v>97847</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,47 +1238,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468660</v>
+        <v>468715</v>
       </c>
       <c r="R7" t="n">
-        <v>6546604</v>
+        <v>6546633</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285801</v>
+        <v>120285804</v>
       </c>
       <c r="B2" t="n">
-        <v>89650</v>
+        <v>97847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468586</v>
+        <v>468660</v>
       </c>
       <c r="R2" t="n">
-        <v>6546480</v>
+        <v>6546604</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285804</v>
+        <v>120285801</v>
       </c>
       <c r="B3" t="n">
-        <v>97847</v>
+        <v>89650</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468660</v>
+        <v>468586</v>
       </c>
       <c r="R3" t="n">
-        <v>6546604</v>
+        <v>6546480</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120285799</v>
+        <v>120285800</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468719</v>
+        <v>468599</v>
       </c>
       <c r="R4" t="n">
-        <v>6546629</v>
+        <v>6546558</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1119,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120285800</v>
+        <v>120285799</v>
       </c>
       <c r="B6" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,31 +1127,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468599</v>
+        <v>468719</v>
       </c>
       <c r="R6" t="n">
-        <v>6546558</v>
+        <v>6546629</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120285805</v>
+        <v>120285801</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468715</v>
+        <v>468586</v>
       </c>
       <c r="R2" t="n">
-        <v>6546633</v>
+        <v>6546480</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -785,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120285804</v>
+        <v>120285802</v>
       </c>
       <c r="B3" t="n">
-        <v>97918</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,31 +792,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468660</v>
+        <v>468607</v>
       </c>
       <c r="R3" t="n">
-        <v>6546604</v>
+        <v>6546581</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -896,43 +887,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120285800</v>
+        <v>120285803</v>
       </c>
       <c r="B4" t="n">
-        <v>56544</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468599</v>
+        <v>468607</v>
       </c>
       <c r="R4" t="n">
-        <v>6546558</v>
+        <v>6546581</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1003,59 +993,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120285803</v>
+        <v>120285805</v>
       </c>
       <c r="B5" t="n">
-        <v>78297</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsmackamossen/Gryteforsmyren, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468607</v>
+        <v>468715</v>
       </c>
       <c r="R5" t="n">
-        <v>6546581</v>
+        <v>6546633</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,15 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120285801</v>
+        <v>120285799</v>
       </c>
       <c r="B6" t="n">
-        <v>89692</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,9 +1131,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468586</v>
+        <v>468719</v>
       </c>
       <c r="R6" t="n">
-        <v>6546480</v>
+        <v>6546629</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,47 +1204,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120285799</v>
+        <v>120285800</v>
       </c>
       <c r="B7" t="n">
-        <v>57332</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468719</v>
+        <v>468599</v>
       </c>
       <c r="R7" t="n">
-        <v>6546629</v>
+        <v>6546558</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1336,15 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120285802</v>
+        <v>120285804</v>
       </c>
       <c r="B8" t="n">
-        <v>94672</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,31 +1317,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468607</v>
+        <v>468660</v>
       </c>
       <c r="R8" t="n">
-        <v>6546581</v>
+        <v>6546604</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 12721-2024 artfynd.xlsx
+++ b/artfynd/A 12721-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120285801</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120285802</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120285803</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120285805</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120285799</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120285800</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,8 +1444,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120285804</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>